--- a/AI Audit Log_NguyenNgocTu.xlsx
+++ b/AI Audit Log_NguyenNgocTu.xlsx
@@ -4,13 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" r:id="rId3"/>
     <sheet name="Week4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week5" sheetId="6" r:id="rId5"/>
+    <sheet name="Week6" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="140">
   <si>
     <t>STT</t>
   </si>
@@ -81,91 +83,1965 @@
     <t>Phản hồi: AI trình bày Session-based Authentication, JWT và OAuth2. Kiểm chứng: Tôi tìm hiểu thêm tài liệu từ documentation và xác nhận JWT phù hợp hơn cho REST API của dự án.</t>
   </si>
   <si>
-    <t>Viết logic xử lý cập nhật trạng thái chỉnh sửa (edit state) trong React và tính toán áp dụng mã giảm giá cho giỏ hàng."</t>
-  </si>
-  <si>
-    <t>"Liệt kê các Use Case cần thiết cho hệ thống quản lý hiệu thuốc (MediCare)."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI đề xuất các use case như xác thực người dùng, quản lý kho thuốc, theo dõi lịch uống thuốc, và quản lý nhân sự. 
-Quyết định: Tôi chọn các chức năng cốt lõi (quản lý kho, tính năng MedicationSchedule để theo dõi tình trạng isTaken hàng ngày) và tạm gác lại các tính năng không ưu tiên ở hiện tại để tập trung hoàn thiện module chính.</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI cung cấp code mẫu quản lý state cho form và hàm tính discountAmount, finalTotal.
-Kiểm chứng: Tôi nhận thấy AI tự ý đổi tên các hằng số (constants) và logic xử lý state startEdit chưa đúng ý đồ. Tôi quyết định tự điều chỉnh lại logic state và nhắc nhở AI giữ nguyên toàn bộ tên biến/hằng số của dự án.</t>
-  </si>
-  <si>
-    <t>"Hướng dẫn gọi API từ frontend React gửi dữ liệu lên backend Node.js."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI đề xuất và viết code mẫu sử dụng thư viện axios để thực hiện các HTTP requests.
-Kiểm chứng: Dựa trên cấu trúc dự án, tôi quyết định không dùng axios mà sử dụng fetch API mặc định để tối ưu và giảm thiểu thư viện bên thứ ba. Tôi đã yêu cầu AI viết lại toàn bộ luồng gọi API bằng fetch.</t>
-  </si>
-  <si>
-    <t>"Cách xây dựng Chatbot RAG sử dụng Google Gemini Embedding API để tự động tư vấn thuốc."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI trình bày luồng hoạt động cơ bản của RAG, cách nhúng dữ liệu (embedding) và truy xuất thông tin.
-Kiểm chứng: Tôi tìm hiểu thêm tài liệu từ Google và đối chiếu với hệ thống hiện tại, sau đó lên kế hoạch thiết kế luồng dữ liệu sao cho tích hợp trơn tru với môi trường Docker và cơ sở dữ liệu PostgreSQL hiện có.</t>
-  </si>
-  <si>
-    <t>x`x`</t>
-  </si>
-  <si>
-    <t>"Viết hàm cấu hình Redis để tối ưu hóa tốc độ truy vấn danh sách sản phẩm thường xuyên từ cơ sở dữ liệu PostgreSQL."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI cung cấp logic kiểm tra dữ liệu trong bộ nhớ đệm trước khi truy vấn database và lưu lại kết quả dưới dạng chuỗi JSON.
-Kiểm chứng: Tôi nhận thấy mã mẫu chưa tối ưu luồng kết nối khi triển khai trong môi trường Docker container. Tôi đã tự điều chỉnh lại hàm quản lý kết nối và giữ nguyên quy chuẩn đặt tên hằng số (const) của hệ thống.</t>
-  </si>
-  <si>
-    <t>Tìm hiểu cách cấu hình hệ số kinh nghiệm (XP Multiplier) và cơ chế ảnh hưởng của các đặc tính nghề nghiệp trong hệ thống game sinh tồn."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI phân tích cấu trúc file cấu hình mã nguồn, giải thích cách tính toán điểm kinh nghiệm và tầm ảnh hưởng của các chỉ số sức khỏe/kỹ năng.
-Kiểm chứng: Tôi đối chiếu thông tin với trải nghiệm thực tế, nhận diện được quy luật vận hành của hệ thống để tự tay chỉnh sửa các thông số thử nghiệm theo đúng ý muốn.</t>
-  </si>
-  <si>
-    <t>"Hướng dẫn cách viết API tải ảnh thuốc/sản phẩm lên Cloudinary trong backend Node.js."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI cung cấp luồng xử lý cơ bản gồm nhận file từ client và gọi SDK của Cloudinary để upload.
-Kiểm chứng: Tôi nhận thấy cần phải xử lý luồng file sao cho tương thích với môi trường Docker hiện tại của dự án. Tôi quyết định tự tinh chỉnh lại cách quản lý bộ nhớ tạm (buffer) và ánh xạ các biến môi trường cấu hình một cách bảo mật.</t>
-  </si>
-  <si>
-    <t>"Giải thích cách triển khai thuật toán mã hóa RSA để bảo mật dữ liệu và tích hợp vào luồng xác thực."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI đưa ra các khái niệm về public/private key và cung cấp thư viện mẫu để thực hiện mã hóa và giải mã dữ liệu.
-Kiểm chứng: Từ phản hồi của AI, tôi nhận diện được quy trình bảo mật cần thiết. Tôi đã tự quyết định cách lưu trữ các khóa bảo mật sao cho tối ưu nhất với cơ sở dữ liệu PostgreSQL và tuân thủ nghiêm ngặt quy tắc đặt tên biến (const) sẵn có của hệ thống.</t>
-  </si>
-  <si>
-    <t>"Giải thích cách dùng cấu trúc ngữ pháp 'not only... but also' và định nghĩa từ 'cooperate' trong tiếng Anh chuyên ngành."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI đưa ra công thức, định nghĩa và các câu ví dụ minh họa cụ thể.
-Kiểm chứng: Tôi đối chiếu với tài liệu học thuật và quyết định ứng dụng trực tiếp các cấu trúc, từ vựng này vào việc viết báo cáo tiến độ/tài liệu cho dự án để nâng cao kỹ năng ngoại ngữ, hỗ trợ mục tiêu đạt GPA 8.0.</t>
-  </si>
-  <si>
-    <t>"Xây dựng luồng xử lý lấy danh sách hóa đơn từ PostgreSQL và hiển thị lên giao diện React."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI cung cấp code React sử dụng các hook cơ bản và sử dụng một số thư viện bên thứ ba để xử lý request.
-Kiểm chứng: Nhắc lại nguyên tắc phát triển, tôi loại bỏ cách làm của AI, tự viết lại luồng gọi API hoàn toàn bằng fetch thuần và điều chỉnh lại state để đảm bảo AI không tự động thay đổi các hằng số (const) tôi đã định nghĩa.</t>
-  </si>
-  <si>
-    <t>"Thiết lập môi trường Docker Compose cho dự án backend bao gồm Node.js, PostgreSQL và pgAdmin."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI cung cấp file cấu hình docker-compose.yml thiết lập các container và biến môi trường cơ bản.
-Quyết định: Tôi giữ lại cấu trúc lõi do AI gợi ý nhưng tự đánh giá và tinh chỉnh lại các tham số về volumes và ports để tương thích chính xác với máy cá nhân, giúp việc quản lý database qua pgAdmin ổn định hơn.</t>
-  </si>
-  <si>
-    <t>"Viết logic tính toán áp dụng hệ thống mã giảm giá (giảm theo % hoặc giảm số tiền cố định) vào tổng tiền ở bước thanh toán."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI viết hàm tính toán trích xuất giá trị và trả về tổng tiền sau khi trừ khuyến mãi.
-Kiểm chứng: Tôi rà soát logic tính toán và tự ánh xạ kết quả vào các biến thực tế của hệ thống (discountAmount, finalTotal). Tôi tiếp tục yêu cầu AI tuân thủ nghiêm ngặt việc không đổi tên các biến/hằng số trong quá trình refactor đoạn code này.</t>
+    <t>Nội dung Prompt/Câu lệnh</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI &amp; Quyết định của người học</t>
+  </si>
+  <si>
+    <t>Xây dựng ý tưởng hệ thống</t>
+  </si>
+  <si>
+    <t>“Tôi muốn xây dựng một hệ thống học trực tuyến (E-learning) đơn giản cho sinh viên. Hãy gợi ý ý tưởng tổng quan, mục tiêu hệ thống và các nhóm người dùng chính.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI gợi ý hệ thống gồm Học viên, Giảng viên, Admin; mục tiêu giúp học tập từ xa, làm bài tập và quản lý khóa học.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chọn phạm vi hệ thống đơn giản, chỉ tập trung vào xem bài giảng và làm trắc nghiệm, không mở rộng sang thanh toán học phí học trực tuyến hay livestream để vừa sức làm bài môn học.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định phạm vi hệ thống</t>
+  </si>
+  <si>
+    <t>“Với hệ thống học trực tuyến cơ bản, hãy liệt kê các chức năng nên có trong phiên bản dành cho đồ án sinh viên.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI liệt kê: Đăng ký/đăng nhập, xem danh sách khóa học, xem video bài giảng, làm quiz trắc nghiệm, giảng viên đăng tải bài học, chấm điểm tự động, admin duyệt khóa học.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi giữ các chức năng cốt lõi phù hợp với yêu cầu bài làm gồm: Đăng nhập, Xem khóa học, Học bài (video/text), Làm quiz, và Giảng viên quản lý nội dung bài học.</t>
+    </r>
+  </si>
+  <si>
+    <t>Decomposition – Chia nhỏ bài toán</t>
+  </si>
+  <si>
+    <t>“Hãy chia hệ thống học trực tuyến này thành các nhóm chức năng nhỏ để tôi dễ vẽ Use Case Diagram.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI chia thành nhóm Người dùng chung (Xác thực), Nhóm Học viên (Student), Nhóm Giảng viên (Teacher) và Nhóm Quản trị (Admin).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi áp dụng cách chia này vì giúp biểu đồ Use Case tường minh, phân định rõ ràng quyền hạn của từng Actor, tránh việc vẽ chồng chéo các chức năng.</t>
+    </r>
+  </si>
+  <si>
+    <t>Abstraction – Lọc thông tin quan trọng</t>
+  </si>
+  <si>
+    <t>“Trong các chức năng của hệ thống E-learning, chức năng nào quan trọng nhất cần đưa vào Use Case Diagram và chức năng nào có thể lược bỏ ở mức sơ đồ tổng quan?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI khuyên giữ lại các tương tác trực tiếp của User như Đăng ký học, Làm bài tập; có thể ẩn các chức năng hệ thống tự chạy như "Tự động sao lưu database" hay "Gửi mail thông báo".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi loại bỏ các chức năng mang tính kỹ thuật ngầm và tập trung hoàn toàn vào các Use Case nghiệp vụ chính hiển thị trên giao diện.</t>
+    </r>
+  </si>
+  <si>
+    <t>Phân tích Actor và Use Case</t>
+  </si>
+  <si>
+    <t>“Hãy liệt kê các Actor và các Use Case tương ứng cho nhóm chức năng của Học viên và Giảng viên.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI liệt kê Học viên có: Xem khóa học, Đăng ký khóa học, Học bài, Làm Quiz. Giảng viên có: Tạo khóa học, Thêm bài học, Xem điểm học viên.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chấp nhận danh sách này vì bám sát quy trình học tập thực tế và đầy đủ vai trò cho một đồ án nhỏ.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định mối quan hệ (Include/Extend)</t>
+  </si>
+  <si>
+    <t>“Trong sơ đồ Use Case của hệ thống này, khi nào thì nên dùng quan hệ &lt;&gt; và &lt;&gt;? Cho ví dụ cụ thể.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI ví dụ: Use case "Làm Quiz" hoặc "Đăng khóa học" &lt;&gt; "Đăng nhập". Chức năng "Làm Quiz" có thể có &lt;&gt; "Xem giải thích đáp án sai" (không bắt buộc).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chọn dùng &lt;&gt; cho Đăng nhập đối với các chức năng cần bảo mật, và tránh lạm dụng &lt;&gt; để sơ đồ không bị rối mắt.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo bản vẽ Mermaid/draw.io</t>
+  </si>
+  <si>
+    <t>“Hãy chuyển Use Case Diagram này sang dạng script Mermaid để tôi xem cấu trúc hoặc hướng dẫn tôi vẽ trên draw.io.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI cung cấp đoạn mã Mermaid phân chia các Actor và các Oval chức năng nằm trong System Boundary.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi dùng đoạn mã của AI để hình dung bố cục, sau đó tự tay kéo thả trên công cụ draw.io để căn chỉnh khoảng cách, chữ nghĩa trực quan và đẹp mắt hơn.</t>
+    </r>
+  </si>
+  <si>
+    <t>Evaluation – Đánh giá diagram</t>
+  </si>
+  <si>
+    <t>“Hãy đánh giá Use Case Diagram của tôi có đúng nguyên tắc không khi tôi đặt database và server thành Actor?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI nhắc nhở: Database và Server là thành phần bên trong/kỹ thuật của hệ thống, không phải là Actor tương tác bên ngoài.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi ngay lập tức loại bỏ các thực thể kỹ thuật như "MySQL Database Server" ra khỏi sơ đồ Use Case, chỉ giữ lại con người (Học viên, Giảng viên, Admin).</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định phạm vi tài liệu SRS</t>
+  </si>
+  <si>
+    <t>“Hãy xác định cấu trúc phạm vi của một tài liệu SRS cho hệ thống học trực tuyến phiên bản cơ bản dành cho sinh viên.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất cấu trúc gồm: Giới thiệu, Mô tả tổng quan, Yêu cầu chức năng (FR), Yêu cầu phi chức năng (NFR), và Ràng buộc hệ thống.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi tuân thủ cấu trúc chuẩn này để hoàn thiện tài liệu SRS, tập trung viết chi tiết phần FR và NFR để làm tiền đề thiết kế database sau này.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định Actor/User Role trong SRS</t>
+  </si>
+  <si>
+    <t>“Hãy mô tả chi tiết vai trò và quyền hạn của Student, Teacher và Admin trong tài liệu SRS hệ thống E-learning.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI viết mô tả: Student (người tiêu thụ nội dung), Teacher (người tạo nội dung và quản lý điểm), Admin (quản lý người dùng và hệ thống).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi đưa phần mô tả quyền hạn này vào chương 2 của SRS nhằm làm rõ ranh giới phân quyền trong mã nguồn ứng dụng sau này.</t>
+    </r>
+  </si>
+  <si>
+    <t>Functional Requirements (FR)</t>
+  </si>
+  <si>
+    <t>“Hãy viết các yêu cầu chức năng cho tính năng 'Làm bài trắc nghiệm (Quiz)' theo chuẩn mã hóa FR-01, FR-02 kèm mô tả.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI tạo danh sách: FR-Quiz-01: Hệ thống hiển thị câu hỏi trắc nghiệm; FR-Quiz-02: Hệ thống tính giờ làm bài; FR-Quiz-03: Hệ thống tự động chấm điểm khi bấm nộp bài.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chọn các yêu cầu này vì tính khả thi cao, lược bỏ bớt phần "FR-Quiz-04: Tự động trộn câu hỏi ngẫu nhiên bằng thuật toán nâng cao" để giảm độ phức tạp cho phiên bản đầu tiên.</t>
+    </r>
+  </si>
+  <si>
+    <t>Non-functional Requirements (NFR)</t>
+  </si>
+  <si>
+    <t>“Hãy đề xuất các yêu cầu phi chức năng (NFR) về hiệu năng, bảo mật và giao diện phù hợp cho một web học trực tuyến nhỏ.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất: Hệ thống tải trang bài học dưới 3 giây, mật khẩu người dùng phải được mã hóa (băm Bcrypt), giao diện hiển thị tốt trên cả máy tính và điện thoại.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi áp dụng các tiêu chí đo lường được này vào mục NFR của SRS để đảm bảo ứng dụng có chất lượng tốt và bảo mật cơ bản.</t>
+    </r>
+  </si>
+  <si>
+    <t>Use Case Description</t>
+  </si>
+  <si>
+    <t>“Hãy viết một bản mô tả Use Case chi tiết cho chức năng 'Đăng ký khóa học (Enroll Course)', gồm các mục Main Flow và Alternative Flow.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI cung cấp cấu trúc chi tiết: Luồng chính (Chọn khóa học -&gt; Bấm Đăng ký -&gt; Hệ thống ghi nhận thành công); Luồng rẽ nhánh (Khóa học đã đăng ký rồi -&gt; Hiển thị cảnh báo).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi kiểm tra lại tính logic của luồng nghiệp vụ này, chỉnh sửa từ ngữ cho khớp với giao diện dự kiến và đưa vào tài liệu đặc tả.</t>
+    </r>
+  </si>
+  <si>
+    <t>System Constraints / Assumptions</t>
+  </si>
+  <si>
+    <t>“Hệ thống học trực tuyến này cần những ràng buộc và giả định gì về mặt môi trường và nghiệp vụ trong SRS?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI gợi ý các ràng buộc: Hệ thống yêu cầu kết nối Internet liên tục để xem video, tệp video bài giảng tải lên không được vượt quá 50MB.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi giữ lại ràng buộc về giới hạn dung lượng file tải lên vì nó rất thực tế đối với việc cấu hình server lưu trữ của sinh viên.</t>
+    </r>
+  </si>
+  <si>
+    <t>Review SRS / Kiểm tra tài liệu</t>
+  </si>
+  <si>
+    <t>“Hãy kiểm tra xem tài liệu SRS của hệ thống E-learning hiện tại có bị mâu thuẫn giữa danh sách chức năng (FR) và sơ đồ Use Case không?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI nhắc nhở rằng trên Use Case có chức năng "Xem lịch sử học tập" nhưng trong danh sách FR chưa hề được định nghĩa.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi tiến hành bổ sung ngay yêu cầu chức năng "FR-User-05: Xem tiến độ và lịch sử học tập" vào tài liệu SRS để đảm bảo tính nhất quán tuyệt đối giữa biểu đồ và văn bản đặc tả.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xây dựng ý tưởng Class</t>
+  </si>
+  <si>
+    <t>“Tôi đang thiết kế Class Diagram cho hệ thống học trực tuyến cơ bản. Dựa trên tài liệu SRS gồm Khóa học, Bài học, Quiz, Thực thể người dùng, hãy xác định các class chính.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất các class thực thể nền tảng: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>User</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Student</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Teacher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Lesson</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Quiz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Question</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Enrollment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi ghi nhận các class này vì chúng phản ánh chính xác các đối tượng cần quản lý dữ liệu trong hệ thống e-learning.</t>
+    </r>
+  </si>
+  <si>
+    <t>Abstraction – Lọc class cần thiết</t>
+  </si>
+  <si>
+    <t>“Trong các class trên, tôi có cần đưa các class như VideoPlayer, UploadButton hay DatabaseConnection vào Class Diagram nghiệp vụ không?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI giải thích: Class Diagram thực thể nên tập trung vào cấu trúc dữ liệu nghiệp vụ, không nên đưa các class giao diện (UI) hoặc các class kết nối hạ tầng vào sơ đồ ở giai đoạn này.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi tinh lọc sơ đồ, loại bỏ toàn bộ các class mang tính giao diện và kết nối kỹ thuật để biểu đồ lớp sạch sẽ, tập trung vào nghiệp vụ quản lý khóa học.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định thuộc tính (Attributes)</t>
+  </si>
+  <si>
+    <t>“Hãy liệt kê thuộc tính cần có cho các class: Course, Lesson và Quiz để đảm bảo đủ thông tin lưu trữ.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI gợi ý: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (courseId, title, description, teacherId); </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Lesson</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (lessonId, title, videoUrl, content, courseId); </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Quiz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (quizId, title, passingScore).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi chuẩn hóa các thuộc tính này, đặt kiểu dữ liệu rõ ràng (String, Integer) và chuẩn bị cho việc ánh xạ sang bảng cơ sở dữ liệu sau này.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định phương thức (Methods)</t>
+  </si>
+  <si>
+    <t>“Hãy đề xuất các phương thức (hành vi) chính cho class Course và Quiz.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> có </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>addLesson()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>removeLesson()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Quiz</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> có </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>addQuestion()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>calculateScore()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi đưa các phương thức nghiệp vụ này vào sơ đồ, lược bỏ các hàm Getter/Setter tự động để tránh làm biểu đồ bị quá dài dòng.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định quan hệ giữa các Class</t>
+  </si>
+  <si>
+    <t>“Hãy phân tích mối quan hệ giữa User với Student/Teacher, và quan hệ giữa Course với Lesson.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI phân tích: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>User</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> là lớp cha, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Student</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Teacher</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> kế thừa (Inheritance) từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>User</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Lesson</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> là quan hệ thành phần (Composition hoặc Aggregation) vì một khóa học chứa nhiều bài học.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi áp dụng quan hệ kế thừa cho thực thể người dùng và quan hệ Aggregation (tập hợp) cho Khóa học - Bài học vì nếu xóa khóa học thì bài học có thể bị xóa theo.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định Multiplicity (Bội số quan hệ)</t>
+  </si>
+  <si>
+    <t>“Hãy chỉ ra bội số (multiplicity) cho quan hệ giữa Student - Course thông qua lớp trung gian Enrollment.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất: Một </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Student</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> có thể có 0..* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Enrollment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, một </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> có thể có 0..* </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Enrollment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">. Mỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Enrollment</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> liên kết chính xác với 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Student</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> và 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi kiểm tra và đồng ý với logic này, đảm bảo thể hiện đúng mối quan hệ nhiều-nhiều giữa Học viên và Khóa học trên sơ đồ.</t>
+    </r>
+  </si>
+  <si>
+    <t>Kiểm tra tính nhất quán với SRS</t>
+  </si>
+  <si>
+    <t>“Hãy kiểm tra xem Class Diagram gồm các thuộc tính và quan hệ đã xây dựng ở tuần 4 có đáp ứng được yêu cầu chức năng 'FR-Quiz-03: Chấm điểm tự động' trong SRS không?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI phát hiện thiếu một class để lưu kết quả làm bài của học viên, đề xuất bổ sung class QuizResult (resultId, studentId, quizId, score, completedAt).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quyết định: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Tôi lập tức bổ sung class QuizResult vào sơ đồ vì nếu thiếu thực thể này, hệ thống sẽ không thể lưu trữ điểm số và lịch sử làm bài của học viên như SRS yêu cầu.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tránh lỗi đặt tên class mơ hồ</t>
+  </si>
+  <si>
+    <t>“Tôi định đặt tên một class xử lý chung là 'LearningManager' hoặc 'DataSystem', tên này có tốt không?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI cảnh báo: Các tên như Manager, System, Data quá chung chung và mơ hồ trong OOP. Nên đặt tên rõ ràng theo thực thể nghiệp vụ.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Tôi loại bỏ ý định dùng tên chung chung, tuân thủ cách đặt tên trực diện: CourseController hoặc giữ nguyên các thực thể thực như Enrollment để quản lý việc đăng ký.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo mã PlantUML cho Class Diagram</t>
+  </si>
+  <si>
+    <t>“Từ danh sách các class User, Student, Teacher, Course, Lesson, Quiz, QuizResult cùng thuộc tính và quan hệ, hãy viết code PlantUML hoàn chỉnh.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI tạo đoạn mã PlantUML chứa đầy đủ cú pháp kế thừa (`&lt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Review tổng thể và sửa lỗi thiết kế</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI nhận xét sơ đồ hiện tại thuần khiết về mặt hướng đối tượng nghiệp vụ, không bị dính các hàm kỹ thuật hay framework cụ thể.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi giữ nguyên thiết kế này để đảm bảo tính độc lập của kiến trúc phần mềm, giúp sơ đồ có thể áp dụng cho cả Java lẫn Node.js nếu cần đổi công nghệ backend.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định đối tượng vẽ State Diagram</t>
+  </si>
+  <si>
+    <t>“Trong hệ thống học trực tuyến (E-learning), đối tượng nào có vòng đời thay đổi trạng thái phức tạp và ý nghĩa nhất để vẽ State Diagram?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI phân tích: Lớp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Khóa học) với các trạng thái từ nháp, chờ duyệt, đã xuất bản, đến lưu trữ; hoặc lớp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>QuizAttempt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Lượt làm bài) là phù hợp nhất.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi quyết định chọn đối tượng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Course</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Khóa học) để vẽ biểu đồ trạng thái, vì nó thể hiện rõ quy trình làm việc giữa Giảng viên (tạo, chỉnh sửa) và Admin (duyệt, hủy).</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định các trạng thái chính (States)</t>
+  </si>
+  <si>
+    <t>“Hãy liệt kê các trạng thái nghiệp vụ có thể có của một Khóa học từ khi khởi tạo đến khi đóng lại.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI đề xuất các trạng thái: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Draft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Bản nháp), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>PendingApproval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Chờ duyệt), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Published</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Đã xuất bản), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Rejected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Bị từ chối), và </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Archived</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> (Lưu trữ/Ẩn).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi giữ lại cả 5 trạng thái này vì chúng bao phủ toàn bộ các tình huống nghiệp vụ thực tế diễn ra trên hệ thống e-learning.</t>
+    </r>
+  </si>
+  <si>
+    <t>Xác định sự kiện và điều kiện chuyển trạng thái</t>
+  </si>
+  <si>
+    <t>“Hãy chỉ ra các Event (Sự kiện) và Guard Condition (Điều kiện ràng buộc) để chuyển một Khóa học từ 'Chờ duyệt' sang 'Đã xuất bản' hoặc 'Bị từ chối'.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI gợi ý: Từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>PendingApproval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; sự kiện </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>approve()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> [nội dung hợp lệ] -&gt; sang </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Published</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">. Sự kiện </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>reject()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> [nội dung vi phạm] -&gt; sang </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Rejected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi đưa các điều kiện ràng buộc nằm trong dấu ngoặc vuông </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>[...]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> này vào sơ đồ để làm rõ điều kiện xử lý logic trong mã nguồn backend.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tránh nhầm lẫn với Activity Diagram</t>
+  </si>
+  <si>
+    <t>“Làm sao để tôi kiểm tra xem State Diagram của tôi có bị vẽ nhầm thành sơ đồ hoạt động (Activity Diagram) ghi lại các bước bấm nút của người dùng không?”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI nhắc nhở: Các nhãn trong ô tròn/chữ nhật của State Diagram phải là Tính từ/Danh từ chỉ trạng thái bền vững của đối tượng (ví dụ: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Published</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">), chứ không phải là Động từ hành động (ví dụ: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Bấm nút lưu</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi kiểm tra lại toàn bộ các nút thắt trên sơ đồ của mình, đảm bảo đặt tên các trạng thái hoàn toàn bằng danh từ/tính từ, còn động từ hành động thì chuyển lên các đường mũi tên giao tiếp (Transitions).</t>
+    </r>
+  </si>
+  <si>
+    <t>Tạo mã PlantUML cho State Diagram</t>
+  </si>
+  <si>
+    <t>“Hãy viết code PlantUML vẽ State Diagram cho thực thể Course với các trạng thái và sự kiện đã thiết kế ở trên, bao gồm điểm bắt đầu và kết thúc.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI cung cấp đoạn mã PlantUML State với các cú pháp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>[*] --&gt; Draft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Draft --&gt; PendingApproval : submitForReview()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>, v.v.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi lấy đoạn mã này, chạy thử trên công cụ hiển thị sơ đồ PlantUML để kiểm tra luồng đi xem có bị bế tắc (deadlock) ở trạng thái nào không. Luồng đi hoàn toàn mượt mà và hợp lý.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tổng hợp lỗi và hoàn thiện Checklist</t>
+  </si>
+  <si>
+    <t>“Hãy liệt kê các lỗi phổ biến khi sinh viên nộp bài State Diagram để tôi làm checklist kiểm tra lần cuối trước khi nộp báo cáo.”</t>
+  </si>
+  <si>
+    <r>
+      <t>Phản hồi:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> AI tổng hợp lỗi: Thiếu trạng thái bắt đầu </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>[*]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>, đặt tên trạng thái bằng động từ hành động, thiếu điều kiện rẽ nhánh ngoại lệ (ví dụ: quên vẽ luồng khi khóa học bị admin từ chối duyệt).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Quyết định:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi dùng danh sách này làm checklist kiểm tra sơ đồ của mình, bổ sung thêm mũi tên từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Rejected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> quay trở lại </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t>Draft</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="163"/>
+      </rPr>
+      <t xml:space="preserve"> để Giảng viên có thể sửa đổi nội dung và nộp duyệt lại. Đây là điểm cải tiến quan trọng giúp sơ đồ logic hơn.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -178,13 +2054,33 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="163"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="163"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="163"/>
     </font>
     <font>
       <b/>
@@ -540,12 +2436,64 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -664,31 +2612,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -697,139 +2633,182 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1172,7 +3151,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="4" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
     <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
@@ -1180,74 +3159,74 @@
     <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="15" spans="1:5">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2"/>
     </row>
     <row r="2" ht="73" customHeight="1" spans="1:5">
-      <c r="A2" s="3">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" ht="55.2" spans="1:5">
-      <c r="A3" s="3">
+    <row r="3" ht="57" spans="1:5">
+      <c r="A3" s="15">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" ht="55.2" spans="1:5">
-      <c r="A4" s="3">
+    <row r="4" ht="57" spans="1:5">
+      <c r="A4" s="15">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" ht="41.4" spans="1:5">
-      <c r="A5" s="3">
+    <row r="5" ht="42.75" spans="1:5">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="18" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1260,8 +3239,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
     <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
@@ -1269,83 +3248,272 @@
     <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>16</v>
+    <row r="1" ht="15.75" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="73.75" customHeight="1" spans="1:5">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:5">
+      <c r="A3" s="13"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" ht="58.5" spans="1:5">
+      <c r="A4" s="13"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1" spans="1:5">
+      <c r="A5" s="13">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:5">
+      <c r="A6" s="13"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" ht="44.25" spans="1:5">
+      <c r="A7" s="13"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:5">
+      <c r="A8" s="13">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" ht="73" customHeight="1" spans="1:5">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:5">
+      <c r="A9" s="13"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="44.25" spans="1:5">
+      <c r="A10" s="13"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1" spans="1:5">
+      <c r="A11" s="13">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" ht="110.4" spans="1:5">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:5">
+      <c r="A12" s="13"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" ht="44.25" spans="1:5">
+      <c r="A13" s="13"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" spans="1:5">
+      <c r="A14" s="13">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:5">
+      <c r="A15" s="13"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" ht="30" spans="1:5">
+      <c r="A16" s="13"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="1:4">
+      <c r="A17" s="13">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:4">
+      <c r="A18" s="13"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" ht="44.25" spans="1:4">
+      <c r="A19" s="13"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" ht="30.75" customHeight="1" spans="1:4">
+      <c r="A20" s="13">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="110.4" spans="1:5">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="110.4" spans="1:5">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="D7" t="s">
-        <v>24</v>
+      <c r="B20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:4">
+      <c r="A21" s="13"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" ht="44.25" spans="1:4">
+      <c r="A22" s="13"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="1:4">
+      <c r="A23" s="13">
+        <v>8</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="1:4">
+      <c r="A24" s="13"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="6"/>
+    </row>
+    <row r="25" ht="44.25" spans="1:4">
+      <c r="A25" s="13"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C23:C25"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1354,8 +3522,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
     <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
@@ -1363,7 +3531,7 @@
     <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" ht="15.75" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1371,70 +3539,245 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" ht="153" customHeight="1" spans="1:5">
+    <row r="2" ht="108" customHeight="1" spans="1:5">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:5">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" ht="44.25" spans="1:5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1" spans="1:5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" ht="44.25" spans="1:5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:5">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="44.25" spans="1:5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1" spans="1:5">
+      <c r="A11" s="3">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" ht="110.4" spans="1:5">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" ht="44.25" spans="1:5">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1" spans="1:5">
+      <c r="A14" s="3">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:5">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" ht="44.25" spans="1:5">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="1:4">
+      <c r="A17" s="3">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:4">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" ht="30" spans="1:4">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="1:4">
+      <c r="A20" s="3">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" ht="110.4" spans="1:5">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" ht="110.4" spans="1:5">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="B20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:4">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="6"/>
+    </row>
+    <row r="22" ht="44.25" spans="1:4">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C20:C22"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1443,8 +3786,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="4" outlineLevelCol="4"/>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
     <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
@@ -1452,7 +3795,7 @@
     <col min="4" max="4" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" ht="15.75" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,70 +3803,581 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" ht="134" customHeight="1" spans="1:5">
+    <row r="2" ht="134.75" customHeight="1" spans="1:5">
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:5">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" ht="30" spans="1:5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1" spans="1:5">
+      <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" ht="44.25" spans="1:5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:5">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="44.25" spans="1:5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" ht="30.75" customHeight="1" spans="1:5">
+      <c r="A11" s="3">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" ht="110.4" spans="1:5">
-      <c r="A3" s="3">
+      <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" ht="44.25" spans="1:5">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" ht="59.25" customHeight="1" spans="1:5">
+      <c r="A14" s="3">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:5">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" ht="44.25" spans="1:5">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="1:4">
+      <c r="A17" s="3">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:4">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" ht="44.25" spans="1:4">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C19"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
+    <col min="3" max="3" width="24.2666666666667" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="59" customHeight="1" spans="1:7">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:7">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" ht="44.25" spans="1:7">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" ht="45" customHeight="1" spans="1:7">
+      <c r="A5" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" ht="110.4" spans="1:5">
-      <c r="A4" s="3">
+      <c r="B5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:7">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" ht="44.25" spans="1:7">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:7">
+      <c r="A8" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" ht="110.4" spans="1:5">
+      <c r="B8" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:7">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="15.75" spans="1:7">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" ht="30.75" customHeight="1" spans="1:7">
+      <c r="A11" s="3">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:7">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" ht="44.25" spans="1:7">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="20.9333333333333" customWidth="1"/>
+    <col min="2" max="2" width="26.8666666666667" customWidth="1"/>
+    <col min="3" max="3" width="24.2666666666667" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" ht="135.5" customHeight="1" spans="1:5">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="3" ht="15" spans="1:5">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="6"/>
+    </row>
+    <row r="4" ht="44.25" spans="1:5">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" ht="45.75" customHeight="1" spans="1:5">
       <c r="A5" s="3">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" ht="15" spans="1:5">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="6"/>
+    </row>
+    <row r="7" ht="44.25" spans="1:5">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" ht="45.75" customHeight="1" spans="1:5">
+      <c r="A8" s="3">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:5">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="6"/>
+    </row>
+    <row r="10" ht="44.25" spans="1:5">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" ht="58.5" customHeight="1" spans="1:5">
+      <c r="A11" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>40</v>
+      <c r="B11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:5">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="6"/>
+    </row>
+    <row r="13" ht="58.5" spans="1:5">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:5">
+      <c r="A14" s="3">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:5">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" ht="44.25" spans="1:5">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" ht="45.75" customHeight="1" spans="1:4">
+      <c r="A17" s="3">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:4">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="6"/>
+    </row>
+    <row r="19" ht="58.5" spans="1:4">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="7" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C17:C19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
